--- a/data/trans_orig/KIDM_C_3_R-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/KIDM_C_3_R-Estudios-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según si se han reído mucho o muchísimo otros menores de él/ella (autopercepción menor) en 2007 (tasa de respuesta: 89,79%)</t>
+          <t>Menores de los/as que se han reído mucho o muchísimo otros/as menores (autopercepción menor) en 2007 (tasa de respuesta: 89,79%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>602</t>
+          <t>597</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4941</t>
+          <t>4984</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>10,89%</t>
+          <t>10,99%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>484</t>
+          <t>481</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>4748</t>
+          <t>4288</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>10,99%</t>
+          <t>9,92%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1242</t>
+          <t>1231</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>7777</t>
+          <t>7321</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>8,78%</t>
+          <t>8,26%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>40419</t>
+          <t>40376</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>44758</t>
+          <t>44763</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>89,11%</t>
+          <t>89,01%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,67%</t>
+          <t>98,68%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>38476</t>
+          <t>38936</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>42740</t>
+          <t>42743</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>89,01%</t>
+          <t>90,08%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,88%</t>
+          <t>98,89%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>80808</t>
+          <t>81264</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>87343</t>
+          <t>87354</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>91,22%</t>
+          <t>91,74%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,6%</t>
+          <t>98,61%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6764</t>
+          <t>6610</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>17009</t>
+          <t>16436</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,93%</t>
+          <t>8,63%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4975</t>
+          <t>4906</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>14456</t>
+          <t>14331</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>6,65%</t>
+          <t>6,59%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>13542</t>
+          <t>13368</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>27961</t>
+          <t>27668</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,86%</t>
+          <t>6,79%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>173377</t>
+          <t>173950</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>183622</t>
+          <t>183776</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>91,07%</t>
+          <t>91,37%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>96,45%</t>
+          <t>96,53%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>202858</t>
+          <t>202983</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>212339</t>
+          <t>212408</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>93,35%</t>
+          <t>93,41%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,71%</t>
+          <t>97,74%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>379738</t>
+          <t>380031</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>394157</t>
+          <t>394331</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>93,14%</t>
+          <t>93,21%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,68%</t>
+          <t>96,72%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>718</t>
+          <t>684</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>6571</t>
+          <t>6365</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>12,11%</t>
+          <t>11,73%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>380</t>
+          <t>637</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>5269</t>
+          <t>4702</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>10,74%</t>
+          <t>9,59%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2111</t>
+          <t>2067</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>9617</t>
+          <t>9623</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>9,31%</t>
+          <t>9,32%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>47675</t>
+          <t>47881</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>53528</t>
+          <t>53562</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>87,89%</t>
+          <t>88,27%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,68%</t>
+          <t>98,74%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>43771</t>
+          <t>44338</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>48660</t>
+          <t>48403</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>89,26%</t>
+          <t>90,41%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,23%</t>
+          <t>98,7%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>93670</t>
+          <t>93664</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>101176</t>
+          <t>101220</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>90,69%</t>
+          <t>90,68%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,96%</t>
+          <t>98,0%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>10234</t>
+          <t>9969</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>22365</t>
+          <t>22453</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,71%</t>
+          <t>7,74%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>8051</t>
+          <t>7628</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>19316</t>
+          <t>18685</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>6,24%</t>
+          <t>6,04%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>20429</t>
+          <t>20944</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>37446</t>
+          <t>37144</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>6,2%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>267627</t>
+          <t>267539</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>279758</t>
+          <t>280023</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>92,29%</t>
+          <t>92,26%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>96,47%</t>
+          <t>96,56%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>290262</t>
+          <t>290893</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>301527</t>
+          <t>301950</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>93,76%</t>
+          <t>93,96%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,4%</t>
+          <t>97,54%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>562125</t>
+          <t>562427</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>579142</t>
+          <t>578627</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>93,75%</t>
+          <t>93,8%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,59%</t>
+          <t>96,51%</t>
         </is>
       </c>
     </row>
@@ -2141,7 +2141,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según si se han reído mucho o muchísimo otros menores de él/ella (autopercepción menor) en 2012 (tasa de respuesta: 95,41%)</t>
+          <t>Menores de los/as que se han reído mucho o muchísimo otros/as menores (autopercepción menor) en 2012 (tasa de respuesta: 95,41%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2336,12 +2336,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3182</t>
+          <t>2737</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>10807</t>
+          <t>10347</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2351,12 +2351,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>6,16%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>20,93%</t>
+          <t>20,04%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2371,12 +2371,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1913</t>
+          <t>1911</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>9893</t>
+          <t>9323</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2386,12 +2386,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>21,9%</t>
+          <t>20,64%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>6136</t>
+          <t>6740</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>17370</t>
+          <t>17503</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2421,12 +2421,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>6,34%</t>
+          <t>6,96%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>17,95%</t>
+          <t>18,08%</t>
         </is>
       </c>
     </row>
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>40819</t>
+          <t>41279</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>48444</t>
+          <t>48889</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2464,12 +2464,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>79,07%</t>
+          <t>79,96%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>93,84%</t>
+          <t>94,7%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>35269</t>
+          <t>35839</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>43249</t>
+          <t>43251</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2499,12 +2499,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>78,1%</t>
+          <t>79,36%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>95,76%</t>
+          <t>95,77%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>79417</t>
+          <t>79284</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>90651</t>
+          <t>90047</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2534,12 +2534,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>82,05%</t>
+          <t>81,92%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>93,66%</t>
+          <t>93,04%</t>
         </is>
       </c>
     </row>
@@ -2679,12 +2679,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>26944</t>
+          <t>26993</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>44511</t>
+          <t>45043</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2694,12 +2694,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>13,49%</t>
+          <t>13,51%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>22,28%</t>
+          <t>22,55%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2714,12 +2714,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>19563</t>
+          <t>19511</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>34392</t>
+          <t>34483</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2729,12 +2729,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>8,75%</t>
+          <t>8,73%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>15,39%</t>
+          <t>15,43%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>51226</t>
+          <t>50979</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>74432</t>
+          <t>74178</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>12,1%</t>
+          <t>12,04%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>17,59%</t>
+          <t>17,53%</t>
         </is>
       </c>
     </row>
@@ -2792,12 +2792,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>155237</t>
+          <t>154705</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>172804</t>
+          <t>172755</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2807,12 +2807,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>77,72%</t>
+          <t>77,45%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>86,51%</t>
+          <t>86,49%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>189112</t>
+          <t>189021</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>203941</t>
+          <t>203993</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2842,12 +2842,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>84,61%</t>
+          <t>84,57%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>91,25%</t>
+          <t>91,27%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>348819</t>
+          <t>349073</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>372025</t>
+          <t>372272</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>82,41%</t>
+          <t>82,47%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>87,9%</t>
+          <t>87,96%</t>
         </is>
       </c>
     </row>
@@ -3022,12 +3022,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2772</t>
+          <t>2776</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>11268</t>
+          <t>10630</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,57%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>18,53%</t>
+          <t>17,48%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3057,12 +3057,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>3452</t>
+          <t>3295</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>11651</t>
+          <t>11180</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>5,97%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>21,11%</t>
+          <t>20,25%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>7836</t>
+          <t>7750</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>19417</t>
+          <t>18938</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>6,75%</t>
+          <t>6,68%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>16,74%</t>
+          <t>16,33%</t>
         </is>
       </c>
     </row>
@@ -3135,12 +3135,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>49533</t>
+          <t>50171</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>58029</t>
+          <t>58025</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>81,47%</t>
+          <t>82,52%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>95,44%</t>
+          <t>95,43%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3170,12 +3170,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>43553</t>
+          <t>44024</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>51752</t>
+          <t>51909</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>78,89%</t>
+          <t>79,75%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>93,75%</t>
+          <t>94,03%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>96588</t>
+          <t>97067</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>108169</t>
+          <t>108255</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>83,26%</t>
+          <t>83,67%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>93,25%</t>
+          <t>93,32%</t>
         </is>
       </c>
     </row>
@@ -3365,12 +3365,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>37239</t>
+          <t>38490</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>58394</t>
+          <t>59050</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>11,93%</t>
+          <t>12,33%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>18,71%</t>
+          <t>18,92%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>28717</t>
+          <t>28856</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>48243</t>
+          <t>48894</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>8,87%</t>
+          <t>8,91%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>14,9%</t>
+          <t>15,1%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>72079</t>
+          <t>72671</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>100496</t>
+          <t>100119</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>11,33%</t>
+          <t>11,43%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>15,8%</t>
+          <t>15,74%</t>
         </is>
       </c>
     </row>
@@ -3478,12 +3478,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>253780</t>
+          <t>253124</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>274935</t>
+          <t>273684</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>81,29%</t>
+          <t>81,08%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>88,07%</t>
+          <t>87,67%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3513,12 +3513,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>275626</t>
+          <t>274975</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>295152</t>
+          <t>295013</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>85,1%</t>
+          <t>84,9%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>91,13%</t>
+          <t>91,09%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>535547</t>
+          <t>535924</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>563964</t>
+          <t>563372</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>84,2%</t>
+          <t>84,26%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>88,67%</t>
+          <t>88,57%</t>
         </is>
       </c>
     </row>
@@ -3744,7 +3744,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según si se han reído mucho o muchísimo otros menores de él/ella (autopercepción menor) en 2016 (tasa de respuesta: 95,77%)</t>
+          <t>Menores de los/as que se han reído mucho o muchísimo otros/as menores (autopercepción menor) en 2016 (tasa de respuesta: 95,77%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3939,12 +3939,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>598</t>
+          <t>630</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5478</t>
+          <t>5945</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3954,12 +3954,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>17,9%</t>
+          <t>19,42%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3974,12 +3974,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>3372</t>
+          <t>2907</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>10813</t>
+          <t>11592</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3989,12 +3989,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>9,2%</t>
+          <t>7,93%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>29,51%</t>
+          <t>31,64%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4009,12 +4009,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>4742</t>
+          <t>4706</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>13795</t>
+          <t>13896</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4024,12 +4024,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>7,05%</t>
+          <t>7,0%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>20,51%</t>
+          <t>20,67%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>25128</t>
+          <t>24661</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>30008</t>
+          <t>29976</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>82,1%</t>
+          <t>80,58%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,05%</t>
+          <t>97,94%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>25825</t>
+          <t>25046</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>33266</t>
+          <t>33731</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>70,49%</t>
+          <t>68,36%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>90,8%</t>
+          <t>92,07%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>53449</t>
+          <t>53348</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>62502</t>
+          <t>62538</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>79,49%</t>
+          <t>79,33%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>92,95%</t>
+          <t>93,0%</t>
         </is>
       </c>
     </row>
@@ -4282,12 +4282,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>15170</t>
+          <t>14867</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>30225</t>
+          <t>30399</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4297,12 +4297,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,22%</t>
+          <t>6,09%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>12,39%</t>
+          <t>12,46%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4317,12 +4317,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>15320</t>
+          <t>15245</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>30554</t>
+          <t>31180</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4332,12 +4332,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>6,46%</t>
+          <t>6,43%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>12,89%</t>
+          <t>13,15%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>34624</t>
+          <t>35183</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>55450</t>
+          <t>57412</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4367,12 +4367,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>7,2%</t>
+          <t>7,31%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>11,53%</t>
+          <t>11,93%</t>
         </is>
       </c>
     </row>
@@ -4395,12 +4395,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>213773</t>
+          <t>213599</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>228828</t>
+          <t>229131</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4410,12 +4410,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>87,61%</t>
+          <t>87,54%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>93,78%</t>
+          <t>93,91%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4430,12 +4430,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>206509</t>
+          <t>205883</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>221743</t>
+          <t>221818</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4445,12 +4445,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>87,11%</t>
+          <t>86,85%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>93,54%</t>
+          <t>93,57%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>425611</t>
+          <t>423649</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>446437</t>
+          <t>445878</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4480,12 +4480,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>88,47%</t>
+          <t>88,07%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>92,8%</t>
+          <t>92,69%</t>
         </is>
       </c>
     </row>
@@ -4625,12 +4625,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>3817</t>
+          <t>3732</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>12757</t>
+          <t>12581</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4640,12 +4640,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>5,37%</t>
+          <t>5,25%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>17,94%</t>
+          <t>17,7%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4660,12 +4660,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>3165</t>
+          <t>3196</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>11814</t>
+          <t>11347</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4675,12 +4675,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>15,65%</t>
+          <t>15,03%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4695,12 +4695,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>8991</t>
+          <t>8694</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>21336</t>
+          <t>20995</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4710,12 +4710,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>6,13%</t>
+          <t>5,93%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>14,55%</t>
+          <t>14,32%</t>
         </is>
       </c>
     </row>
@@ -4738,12 +4738,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>58333</t>
+          <t>58509</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>67273</t>
+          <t>67358</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>82,06%</t>
+          <t>82,3%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>94,63%</t>
+          <t>94,75%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4773,12 +4773,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>63688</t>
+          <t>64155</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>72337</t>
+          <t>72306</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4788,12 +4788,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>84,35%</t>
+          <t>84,97%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>95,81%</t>
+          <t>95,77%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4808,12 +4808,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>125256</t>
+          <t>125597</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>137601</t>
+          <t>137898</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4823,12 +4823,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>85,45%</t>
+          <t>85,68%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>93,87%</t>
+          <t>94,07%</t>
         </is>
       </c>
     </row>
@@ -4968,12 +4968,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>22477</t>
+          <t>23288</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>40964</t>
+          <t>41274</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4983,12 +4983,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>6,74%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>11,85%</t>
+          <t>11,94%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5003,12 +5003,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>26171</t>
+          <t>26540</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>44589</t>
+          <t>45214</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5018,12 +5018,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>7,49%</t>
+          <t>7,6%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>12,77%</t>
+          <t>12,95%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5038,12 +5038,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>54592</t>
+          <t>54564</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>79978</t>
+          <t>79629</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5053,12 +5053,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>7,86%</t>
+          <t>7,85%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>11,51%</t>
+          <t>11,46%</t>
         </is>
       </c>
     </row>
@@ -5081,12 +5081,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>304730</t>
+          <t>304420</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>323217</t>
+          <t>322406</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5096,12 +5096,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>88,15%</t>
+          <t>88,06%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>93,5%</t>
+          <t>93,26%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>304614</t>
+          <t>303989</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>323032</t>
+          <t>322663</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5131,12 +5131,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>87,23%</t>
+          <t>87,05%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>92,51%</t>
+          <t>92,4%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5151,12 +5151,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>614919</t>
+          <t>615268</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>640305</t>
+          <t>640333</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5166,12 +5166,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>88,49%</t>
+          <t>88,54%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>92,14%</t>
+          <t>92,15%</t>
         </is>
       </c>
     </row>
@@ -5347,7 +5347,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según si se han reído mucho o muchísimo otros menores de él/ella (autopercepción menor) en 2023 (tasa de respuesta: 99,65%)</t>
+          <t>Menores de los/as que se han reído mucho o muchísimo otros/as menores (autopercepción menor) en 2023 (tasa de respuesta: 99,65%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3787</t>
+          <t>3593</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>13820</t>
+          <t>14751</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -5900,12 +5900,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,67%</t>
+          <t>9,26%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5920,12 +5920,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1680</t>
+          <t>1634</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>9872</t>
+          <t>9678</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5935,12 +5935,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5955,12 +5955,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>7313</t>
+          <t>7297</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>20232</t>
+          <t>19929</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5970,12 +5970,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,61%</t>
+          <t>5,52%</t>
         </is>
       </c>
     </row>
@@ -5998,12 +5998,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>145493</t>
+          <t>144562</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>155526</t>
+          <t>155720</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6013,12 +6013,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>91,33%</t>
+          <t>90,74%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,62%</t>
+          <t>97,74%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>191649</t>
+          <t>191843</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>199841</t>
+          <t>199887</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6048,12 +6048,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>95,1%</t>
+          <t>95,2%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,17%</t>
+          <t>99,19%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>340601</t>
+          <t>340904</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>353520</t>
+          <t>353536</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6083,12 +6083,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>94,39%</t>
+          <t>94,48%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,97%</t>
+          <t>97,98%</t>
         </is>
       </c>
     </row>
@@ -6268,7 +6268,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>3378</t>
+          <t>3016</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6283,7 +6283,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,41%</t>
+          <t>5,72%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6303,7 +6303,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>3440</t>
+          <t>2972</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6318,7 +6318,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>3,25%</t>
         </is>
       </c>
     </row>
@@ -6376,7 +6376,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>49315</t>
+          <t>49677</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -6391,7 +6391,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>93,59%</t>
+          <t>94,28%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -6411,7 +6411,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>88005</t>
+          <t>88473</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -6426,7 +6426,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,24%</t>
+          <t>96,75%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -6571,12 +6571,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3597</t>
+          <t>3869</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>13483</t>
+          <t>14270</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6586,12 +6586,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,41%</t>
+          <t>6,78%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6606,12 +6606,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2144</t>
+          <t>2142</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>10486</t>
+          <t>10620</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6626,7 +6626,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>3,92%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6641,12 +6641,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>8490</t>
+          <t>7381</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>21475</t>
+          <t>20811</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6656,12 +6656,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,32%</t>
         </is>
       </c>
     </row>
@@ -6684,12 +6684,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>196989</t>
+          <t>196202</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>206875</t>
+          <t>206603</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6699,12 +6699,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>93,59%</t>
+          <t>93,22%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,29%</t>
+          <t>98,16%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6719,12 +6719,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>260482</t>
+          <t>260348</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>268824</t>
+          <t>268826</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6734,7 +6734,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>96,13%</t>
+          <t>96,08%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -6754,12 +6754,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>459965</t>
+          <t>460629</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>472950</t>
+          <t>474059</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6769,12 +6769,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>95,54%</t>
+          <t>95,68%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,24%</t>
+          <t>98,47%</t>
         </is>
       </c>
     </row>
